--- a/teachers/teacher_classlist.xlsx
+++ b/teachers/teacher_classlist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\school\teachers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F73464C7-A8AA-4546-BDC5-73FAEFF85501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19DA2930-D1DD-4DFA-950A-1C9706C57F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B0EE3A1B-6606-404C-A613-B507AB0AC220}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{7360611D-B03A-4614-820B-EE9D4F28EABE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,13 +42,13 @@
     <t>lesson</t>
   </si>
   <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>finish_date</t>
+  </si>
+  <si>
     <t>day</t>
-  </si>
-  <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>finish_date</t>
   </si>
   <si>
     <t>class_start</t>
@@ -411,8 +411,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D80E38-FE9F-4451-BE70-991BD23B5136}">
-  <dimension ref="A1:M1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF4D8EE-97AD-4AC4-9DDB-21007BB61286}">
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -424,15 +424,15 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2" t="s">
@@ -444,9 +444,149 @@
       </c>
       <c r="M1" s="2"/>
     </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="48">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
     <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
